--- a/boletas_extraidas.xlsx
+++ b/boletas_extraidas.xlsx
@@ -471,8 +471,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL GASTRONOMICA
-CACHAPA LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL GASTRONOMICA CACHAPA LIMITADA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -497,11 +496,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Pago Cuentas</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
